--- a/output/stock_quant_scores/ASML_income_df.xlsx
+++ b/output/stock_quant_scores/ASML_income_df.xlsx
@@ -1190,7 +1190,9 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>6760100000</v>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1201,10 +1203,14 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>14.36</v>
+      </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
+      <c r="Y6" t="n">
+        <v>5883200000</v>
+      </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
@@ -1224,9 +1230,13 @@
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>9809000000</v>
+      </c>
       <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>18611000000</v>
+      </c>
       <c r="AT6" t="inlineStr"/>
     </row>
   </sheetData>
